--- a/vignettes/vignette-1/donor_selection.xlsx
+++ b/vignettes/vignette-1/donor_selection.xlsx
@@ -522,32 +522,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2008_2018</t>
+          <t>1880_2024</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2008</v>
+        <v>1880</v>
       </c>
       <c r="D3" t="n">
-        <v>2018</v>
+        <v>2024</v>
       </c>
       <c r="E3" t="n">
-        <v>369.552</v>
+        <v>480.668</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002</v>
+        <v>24.73</v>
       </c>
       <c r="G3" t="n">
-        <v>5.411958262977875e-06</v>
+        <v>0.05144923315053217</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9613437180064304</v>
+        <v>0.9127510204081632</v>
       </c>
       <c r="I3" t="n">
-        <v>0.977604</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.302317</v>
+        <v>-0.039431</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>

--- a/vignettes/vignette-1/donor_selection.xlsx
+++ b/vignettes/vignette-1/donor_selection.xlsx
@@ -500,10 +500,10 @@
         <v>0.08254341213769573</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2084905273431778</v>
+        <v>0.208501683533215</v>
       </c>
       <c r="I2" t="n">
-        <v>0.596156</v>
+        <v>0.595927</v>
       </c>
       <c r="J2" t="n">
         <v>-2.085266</v>
@@ -522,32 +522,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1880_2024</t>
+          <t>1910_2019</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1880</v>
+        <v>1910</v>
       </c>
       <c r="D3" t="n">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="E3" t="n">
-        <v>480.668</v>
+        <v>416.6</v>
       </c>
       <c r="F3" t="n">
-        <v>24.73</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05144923315053217</v>
+        <v>0.01200192030724916</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9127510204081632</v>
+        <v>0.9803474363986653</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0.974776</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.039431</v>
+        <v>-0.182482</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>

--- a/vignettes/vignette-1/donor_selection.xlsx
+++ b/vignettes/vignette-1/donor_selection.xlsx
@@ -522,32 +522,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1910_2019</t>
+          <t>1884_2022</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1910</v>
+        <v>1884</v>
       </c>
       <c r="D3" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="E3" t="n">
-        <v>416.6</v>
+        <v>642.193</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>9.1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01200192030724916</v>
+        <v>0.01417019494139612</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9803474363986653</v>
+        <v>0.9802235265502031</v>
       </c>
       <c r="I3" t="n">
-        <v>0.974776</v>
+        <v>0.977397</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.182482</v>
+        <v>0.250281</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>

--- a/vignettes/vignette-1/donor_selection.xlsx
+++ b/vignettes/vignette-1/donor_selection.xlsx
@@ -481,32 +481,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3334_2017</t>
+          <t>2001_2017</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3334</v>
+        <v>2001</v>
       </c>
       <c r="D2" t="n">
         <v>2017</v>
       </c>
       <c r="E2" t="n">
-        <v>62.137</v>
+        <v>2068</v>
       </c>
       <c r="F2" t="n">
-        <v>5.129</v>
+        <v>111.3</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08254341213769573</v>
+        <v>0.05382011605415861</v>
       </c>
       <c r="H2" t="n">
-        <v>0.208501683533215</v>
+        <v>0.2095021040019395</v>
       </c>
       <c r="I2" t="n">
-        <v>0.595927</v>
+        <v>0.720813</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.085266</v>
+        <v>1.419729</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
